--- a/tools/importer/reports/import-product-listing-page.report.xlsx
+++ b/tools/importer/reports/import-product-listing-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="214">
   <si>
     <t>_reportFile</t>
   </si>
@@ -43,21 +43,42 @@
     <t>url</t>
   </si>
   <si>
+    <t>en-us/lp/dell-video-conferencing-room-solutions.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards","cards","columns","columns","columns","tabs","tabs","carousel"]</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>en-us/lp/dell-video-conferencing-room-solutions</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>cp-landing-page</t>
+  </si>
+  <si>
+    <t>2026-03-20T16:06:10.806Z</t>
+  </si>
+  <si>
+    <t>Dell Video Conferencing Room Solutions | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dell-video-conferencing-room-solutions</t>
+  </si>
+  <si>
     <t>en-us/lp/disaggregated-infrastructure.report.json</t>
   </si>
   <si>
     <t>["hero","cards","cards","cards","cards"]</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>en-us/lp/disaggregated-infrastructure</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>solutions-landing-page</t>
   </si>
   <si>
@@ -88,6 +109,24 @@
     <t>https://www.dell.com/en-us/lp/enterprise-upgrades</t>
   </si>
   <si>
+    <t>en-us/lp/thin-client-solutions.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards","tabs","tabs","carousel","carousel"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/thin-client-solutions</t>
+  </si>
+  <si>
+    <t>2026-03-20T16:06:16.879Z</t>
+  </si>
+  <si>
+    <t>Dell Thin Clients &amp; Secure Cloud Client Workspaces | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/thin-client-solutions</t>
+  </si>
+  <si>
     <t>en-us/lp/dt/artificial-intelligence-services.report.json</t>
   </si>
   <si>
@@ -403,7 +442,7 @@
     <t>en-us/shop/dell-laptops/scr/laptops.report.json</t>
   </si>
   <si>
-    <t>["hero","cards","accordion"]</t>
+    <t>["hero"]</t>
   </si>
   <si>
     <t>en-us/shop/dell-laptops/scr/laptops</t>
@@ -412,7 +451,7 @@
     <t>product-listing-page</t>
   </si>
   <si>
-    <t>2026-03-20T16:03:37.890Z</t>
+    <t>2026-03-20T17:12:46.418Z</t>
   </si>
   <si>
     <t>Dell Laptops - Shop Work, Gaming &amp; Student PCs | Dell USA</t>
@@ -421,19 +460,55 @@
     <t>https://www.dell.com/en-us/shop/dell-laptops/scr/laptops</t>
   </si>
   <si>
+    <t>en-us/shop/dell-pro-max-pcs-and-workstations/sc/workstations.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/shop/dell-pro-max-pcs-and-workstations/sc/workstations</t>
+  </si>
+  <si>
+    <t>system-category-page</t>
+  </si>
+  <si>
+    <t>2026-03-20T16:06:00.858Z</t>
+  </si>
+  <si>
+    <t>Dell Pro Max PCs and Workstations | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/shop/dell-pro-max-pcs-and-workstations/sc/workstations</t>
+  </si>
+  <si>
     <t>en-us/shop/desktop-computers/scr/desktops.report.json</t>
   </si>
   <si>
     <t>en-us/shop/desktop-computers/scr/desktops</t>
   </si>
   <si>
-    <t>2026-03-20T16:03:48.925Z</t>
+    <t>2026-03-20T17:12:56.973Z</t>
   </si>
   <si>
     <t>Dell Desktop Computer- Best Dell PCs &amp; Personal Computers | Dell USA</t>
   </si>
   <si>
     <t>https://www.dell.com/en-us/shop/desktop-computers/scr/desktops</t>
+  </si>
+  <si>
+    <t>en-us/shop/gaming-laptops-pcs-and-accessories/sc/game.report.json</t>
+  </si>
+  <si>
+    <t>en-us/shop/gaming-laptops-pcs-and-accessories/sc/game</t>
+  </si>
+  <si>
+    <t>2026-03-20T16:05:54.704Z</t>
+  </si>
+  <si>
+    <t>Dell Gaming Laptops, PCs, &amp; Accessories | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/shop/gaming-laptops-pcs-and-accessories/sc/game</t>
   </si>
   <si>
     <t>en-us/shop/scc/sc/apex.report.json</t>
@@ -506,7 +581,7 @@
     <t>en-us/shop/scc/sc/laptops</t>
   </si>
   <si>
-    <t>2026-03-20T16:03:27.524Z</t>
+    <t>2026-03-20T17:12:36.685Z</t>
   </si>
   <si>
     <t>https://www.dell.com/en-us/shop/scc/sc/laptops</t>
@@ -970,11 +1045,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="1" max="5" width="50" customWidth="1"/>
     <col min="7" max="7" width="24" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
     <col min="9" max="10" width="50" customWidth="1"/>
@@ -1064,24 +1138,24 @@
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
@@ -1090,13 +1164,13 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H4" t="s">
         <v>29</v>
@@ -1128,39 +1202,39 @@
         <v>14</v>
       </c>
       <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
         <v>35</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>36</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>37</v>
-      </c>
-      <c r="J5" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
         <v>39</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
         <v>41</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
       </c>
       <c r="H6" t="s">
         <v>42</v>
@@ -1192,24 +1266,24 @@
         <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
@@ -1218,30 +1292,30 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="H8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
@@ -1250,13 +1324,13 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="H9" t="s">
         <v>61</v>
@@ -1288,7 +1362,7 @@
         <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H10" t="s">
         <v>67</v>
@@ -1320,24 +1394,24 @@
         <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="H11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
@@ -1346,30 +1420,30 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="H12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
@@ -1378,30 +1452,30 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
@@ -1410,30 +1484,30 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="H14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
@@ -1442,30 +1516,30 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
@@ -1474,30 +1548,30 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="H16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
@@ -1506,13 +1580,13 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F17" t="s">
         <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="H17" t="s">
         <v>109</v>
@@ -1529,7 +1603,7 @@
         <v>112</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>113</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
@@ -1538,30 +1612,30 @@
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F18" t="s">
         <v>14</v>
       </c>
       <c r="G18" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="H18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
@@ -1570,30 +1644,30 @@
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F19" t="s">
         <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="H19" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I19" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J19" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B20" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
@@ -1602,30 +1676,30 @@
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F20" t="s">
         <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="H20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
@@ -1634,13 +1708,13 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F21" t="s">
         <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="H21" t="s">
         <v>133</v>
@@ -1657,7 +1731,7 @@
         <v>136</v>
       </c>
       <c r="B22" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
@@ -1666,30 +1740,30 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F22" t="s">
         <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="H22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B23" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -1698,62 +1772,62 @@
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F23" t="s">
         <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="C24" t="s">
-        <v>149</v>
+        <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="E24" t="s">
         <v>151</v>
       </c>
       <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
         <v>152</v>
-      </c>
-      <c r="G24" t="s">
-        <v>12</v>
       </c>
       <c r="H24" t="s">
         <v>153</v>
       </c>
       <c r="I24" t="s">
-        <v>12</v>
+        <v>154</v>
       </c>
       <c r="J24" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B25" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
@@ -1768,7 +1842,7 @@
         <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H25" t="s">
         <v>158</v>
@@ -1785,7 +1859,7 @@
         <v>161</v>
       </c>
       <c r="B26" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
@@ -1800,24 +1874,24 @@
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="H26" t="s">
         <v>163</v>
       </c>
       <c r="I26" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="J26" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B27" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -1826,62 +1900,62 @@
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F27" t="s">
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="H27" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I27" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J27" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B28" t="s">
-        <v>172</v>
+        <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="D28" t="s">
-        <v>12</v>
+        <v>175</v>
       </c>
       <c r="E28" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>177</v>
       </c>
       <c r="G28" t="s">
-        <v>144</v>
+        <v>12</v>
       </c>
       <c r="H28" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="I28" t="s">
-        <v>175</v>
+        <v>12</v>
       </c>
       <c r="J28" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B29" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C29" t="s">
         <v>12</v>
@@ -1890,30 +1964,30 @@
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="H29" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I29" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="J29" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B30" t="s">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
@@ -1922,22 +1996,150 @@
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H30" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I30" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="J30" t="s">
-        <v>188</v>
+        <v>189</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>190</v>
+      </c>
+      <c r="B31" t="s">
+        <v>191</v>
+      </c>
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" t="s">
+        <v>192</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s">
+        <v>169</v>
+      </c>
+      <c r="H31" t="s">
+        <v>193</v>
+      </c>
+      <c r="I31" t="s">
+        <v>194</v>
+      </c>
+      <c r="J31" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>196</v>
+      </c>
+      <c r="B32" t="s">
+        <v>197</v>
+      </c>
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" t="s">
+        <v>198</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" t="s">
+        <v>169</v>
+      </c>
+      <c r="H32" t="s">
+        <v>199</v>
+      </c>
+      <c r="I32" t="s">
+        <v>200</v>
+      </c>
+      <c r="J32" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>202</v>
+      </c>
+      <c r="B33" t="s">
+        <v>203</v>
+      </c>
+      <c r="C33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" t="s">
+        <v>204</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" t="s">
+        <v>169</v>
+      </c>
+      <c r="H33" t="s">
+        <v>205</v>
+      </c>
+      <c r="I33" t="s">
+        <v>206</v>
+      </c>
+      <c r="J33" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>208</v>
+      </c>
+      <c r="B34" t="s">
+        <v>209</v>
+      </c>
+      <c r="C34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" t="s">
+        <v>210</v>
+      </c>
+      <c r="F34" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" t="s">
+        <v>169</v>
+      </c>
+      <c r="H34" t="s">
+        <v>211</v>
+      </c>
+      <c r="I34" t="s">
+        <v>212</v>
+      </c>
+      <c r="J34" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>
